--- a/data/trans_dic/P02E$otras-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 17,61</t>
+          <t>6,02; 17,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,73</t>
+          <t>1,92; 9,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,17; 10,83</t>
+          <t>3,13; 10,67</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,64</t>
+          <t>5,06; 12,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 10,85</t>
+          <t>4,68; 11,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 13,15</t>
+          <t>4,81; 11,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,59; 13,29</t>
+          <t>6,69; 13,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,67</t>
+          <t>4,35; 8,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,33</t>
+          <t>4,64; 10,05</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 10,82</t>
+          <t>3,95; 11,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,81</t>
+          <t>2,36; 6,66</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 6,26</t>
+          <t>1,29; 6,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,68</t>
+          <t>4,11; 10,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,86; 8,39</t>
+          <t>3,84; 8,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 12,25</t>
+          <t>6,19; 12,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,61; 8,88</t>
+          <t>4,54; 9,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,65; 6,92</t>
+          <t>3,47; 6,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,17</t>
+          <t>4,85; 9,05</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,61; 16,79</t>
+          <t>5,41; 16,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 8,26</t>
+          <t>2,58; 8,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,85</t>
+          <t>1,89; 8,83</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 11,46</t>
+          <t>4,35; 11,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,28</t>
+          <t>2,14; 6,47</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 13,1</t>
+          <t>5,57; 13,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 12,27</t>
+          <t>6,07; 12,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,16</t>
+          <t>2,62; 6,07</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,66</t>
+          <t>4,77; 9,99</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,74; 11,18</t>
+          <t>3,68; 10,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 11,68</t>
+          <t>4,57; 11,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,05; 11,57</t>
+          <t>3,88; 11,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,56</t>
+          <t>1,14; 5,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,12</t>
+          <t>2,92; 6,93</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 16,21</t>
+          <t>8,44; 15,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,56</t>
+          <t>2,63; 6,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,03; 7,58</t>
+          <t>4,21; 7,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,33; 12,95</t>
+          <t>7,45; 12,96</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,39</t>
+          <t>6,35; 10,68</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,82; 6,81</t>
+          <t>3,87; 6,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 6,75</t>
+          <t>3,61; 6,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,68</t>
+          <t>4,85; 7,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,66</t>
+          <t>4,17; 6,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 11,36</t>
+          <t>7,81; 11,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,26</t>
+          <t>5,69; 8,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,34</t>
+          <t>4,36; 6,24</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,51; 9,09</t>
+          <t>6,54; 9,16</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7518; 23103</t>
+          <t>7904; 23183</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4113; 17358</t>
+          <t>3824; 19058</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5091; 17369</t>
+          <t>5027; 17116</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11595; 27814</t>
+          <t>11129; 27707</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>14203; 32366</t>
+          <t>13956; 32926</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8955; 25877</t>
+          <t>9467; 23418</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23142; 46670</t>
+          <t>23494; 45810</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20838; 43105</t>
+          <t>21610; 43475</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17171; 36911</t>
+          <t>16588; 35917</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6962; 21296</t>
+          <t>7779; 21717</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6949; 20669</t>
+          <t>7162; 20235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3821; 14876</t>
+          <t>3068; 14911</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12175; 29620</t>
+          <t>12578; 31731</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17664; 38397</t>
+          <t>17559; 38253</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21818; 43884</t>
+          <t>22165; 44319</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23207; 44653</t>
+          <t>22818; 45475</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27819; 52691</t>
+          <t>26422; 51583</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>29016; 54665</t>
+          <t>28914; 53963</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>7163; 21451</t>
+          <t>6908; 21046</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5674; 18229</t>
+          <t>5697; 18300</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3092; 14522</t>
+          <t>3098; 14484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8779; 22652</t>
+          <t>8605; 23164</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7980; 22269</t>
+          <t>7577; 22947</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13864; 33248</t>
+          <t>14151; 33874</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19672; 39923</t>
+          <t>19746; 40229</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15658; 35421</t>
+          <t>15060; 34896</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19937; 40347</t>
+          <t>19933; 41739</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6378; 19051</t>
+          <t>6269; 18188</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11673; 30561</t>
+          <t>11962; 30042</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7872; 22502</t>
+          <t>7551; 21628</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3349; 15675</t>
+          <t>3203; 14650</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11729; 28899</t>
+          <t>11838; 28152</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25501; 48974</t>
+          <t>25517; 47622</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11851; 29672</t>
+          <t>11911; 28623</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26912; 50627</t>
+          <t>28142; 53190</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>36380; 64310</t>
+          <t>37014; 64355</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38959; 65075</t>
+          <t>39746; 66857</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>37619; 67032</t>
+          <t>38149; 66076</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27861; 51102</t>
+          <t>27325; 52759</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>46801; 77212</t>
+          <t>48783; 77764</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63709; 100977</t>
+          <t>63294; 98066</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85700; 126184</t>
+          <t>86790; 125425</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>93071; 134732</t>
+          <t>92870; 134030</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>110604; 158601</t>
+          <t>109007; 156063</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>121619; 169745</t>
+          <t>122174; 171046</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 17,67</t>
+          <t>6,06; 17,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,59</t>
+          <t>1,97; 8,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 10,67</t>
+          <t>3,14; 11,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 12,6</t>
+          <t>5,17; 12,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,68; 11,03</t>
+          <t>4,53; 10,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 11,9</t>
+          <t>4,57; 11,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,69; 13,04</t>
+          <t>6,54; 12,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,74</t>
+          <t>4,29; 8,85</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 10,05</t>
+          <t>4,9; 10,05</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,95; 11,03</t>
+          <t>3,61; 11,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,66</t>
+          <t>2,34; 7,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,27</t>
+          <t>1,29; 6,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,37</t>
+          <t>4,09; 9,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,35</t>
+          <t>3,78; 8,34</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 12,37</t>
+          <t>6,2; 12,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,54; 9,04</t>
+          <t>4,86; 8,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 6,77</t>
+          <t>3,65; 6,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,05</t>
+          <t>4,81; 8,97</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 16,48</t>
+          <t>5,44; 16,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 8,29</t>
+          <t>2,53; 8,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 8,83</t>
+          <t>1,89; 8,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,72</t>
+          <t>4,41; 12,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,47</t>
+          <t>2,29; 6,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 13,34</t>
+          <t>5,76; 13,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,07; 12,37</t>
+          <t>5,71; 11,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,07</t>
+          <t>2,88; 6,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 9,99</t>
+          <t>4,77; 9,81</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 10,68</t>
+          <t>3,56; 10,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 11,48</t>
+          <t>4,5; 11,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 11,12</t>
+          <t>3,96; 11,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,19</t>
+          <t>1,15; 5,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,92; 6,93</t>
+          <t>2,82; 7,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 15,76</t>
+          <t>8,5; 15,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,32</t>
+          <t>2,68; 6,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,21; 7,97</t>
+          <t>4,18; 7,72</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 12,96</t>
+          <t>7,31; 12,74</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,68</t>
+          <t>6,14; 10,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,87; 6,71</t>
+          <t>3,9; 6,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,97</t>
+          <t>3,73; 6,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,73</t>
+          <t>4,87; 7,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,46</t>
+          <t>4,21; 6,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,29</t>
+          <t>7,65; 11,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,21</t>
+          <t>5,68; 8,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,24</t>
+          <t>4,44; 6,25</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 9,16</t>
+          <t>6,58; 8,95</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7904; 23183</t>
+          <t>7951; 22436</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3824; 19058</t>
+          <t>3910; 17454</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5027; 17116</t>
+          <t>5041; 17869</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11129; 27707</t>
+          <t>11367; 28343</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13956; 32926</t>
+          <t>13520; 31811</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9467; 23418</t>
+          <t>8990; 23251</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23494; 45810</t>
+          <t>22965; 43745</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21610; 43475</t>
+          <t>21331; 43984</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16588; 35917</t>
+          <t>17486; 35901</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7779; 21717</t>
+          <t>7105; 21890</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7162; 20235</t>
+          <t>7113; 22185</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3068; 14911</t>
+          <t>3063; 14671</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12578; 31731</t>
+          <t>12517; 29810</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>17559; 38253</t>
+          <t>17297; 38187</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22165; 44319</t>
+          <t>22208; 44043</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22818; 45475</t>
+          <t>24435; 44739</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26422; 51583</t>
+          <t>27771; 52637</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>28914; 53963</t>
+          <t>28638; 53481</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6908; 21046</t>
+          <t>6951; 20892</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5697; 18300</t>
+          <t>5578; 18314</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3098; 14484</t>
+          <t>3095; 14446</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8605; 23164</t>
+          <t>8708; 23839</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>7577; 22947</t>
+          <t>8121; 22079</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14151; 33874</t>
+          <t>14622; 33460</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19746; 40229</t>
+          <t>18589; 38166</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15060; 34896</t>
+          <t>16587; 36032</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19933; 41739</t>
+          <t>19921; 40982</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6269; 18188</t>
+          <t>6073; 17812</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11962; 30042</t>
+          <t>11776; 28892</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7551; 21628</t>
+          <t>7699; 21846</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3203; 14650</t>
+          <t>3237; 14868</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11838; 28152</t>
+          <t>11466; 29290</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>25517; 47622</t>
+          <t>25695; 47670</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11911; 28623</t>
+          <t>12119; 28466</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>28142; 53190</t>
+          <t>27880; 51558</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37014; 64355</t>
+          <t>36316; 63276</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>39746; 66857</t>
+          <t>38436; 66471</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>38149; 66076</t>
+          <t>38440; 67796</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>27325; 52759</t>
+          <t>28249; 52097</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>48783; 77764</t>
+          <t>48958; 79429</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>63294; 98066</t>
+          <t>63874; 100401</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86790; 125425</t>
+          <t>85011; 125404</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>92870; 134030</t>
+          <t>92771; 134876</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>109007; 156063</t>
+          <t>111033; 156376</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>122174; 171046</t>
+          <t>122813; 167237</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
